--- a/data/matches/leagues/Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/matches/leagues/Germany_Bundesliga_2_2025-2026.xlsx
@@ -53413,22 +53413,22 @@
         <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R112" t="n">
         <v>9</v>
       </c>
       <c r="S112" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T112" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U112" t="n">
         <v>11</v>
       </c>
       <c r="V112" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W112" t="n">
         <v>17</v>
@@ -53600,13 +53600,13 @@
         <v>23</v>
       </c>
       <c r="BZ112" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="CA112" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="CB112" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="CC112" t="n">
         <v>0</v>
@@ -54130,7 +54130,7 @@
         <v>5</v>
       </c>
       <c r="CV113" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CW113" t="n">
         <v>1</v>
@@ -54375,7 +54375,7 @@
         <v>14</v>
       </c>
       <c r="W114" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X114" t="n">
         <v>20</v>
@@ -54835,13 +54835,13 @@
         <v>8</v>
       </c>
       <c r="S115" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T115" t="n">
         <v>6</v>
       </c>
       <c r="U115" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V115" t="n">
         <v>14</v>
@@ -54853,10 +54853,10 @@
         <v>9</v>
       </c>
       <c r="Y115" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Z115" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
@@ -55016,13 +55016,13 @@
         <v>29</v>
       </c>
       <c r="BZ115" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="CA115" t="n">
         <v>1.65</v>
       </c>
       <c r="CB115" t="n">
-        <v>3.65</v>
+        <v>3.59</v>
       </c>
       <c r="CC115" t="n">
         <v>0</v>

--- a/data/matches/leagues/Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/matches/leagues/Germany_Bundesliga_2_2025-2026.xlsx
@@ -57698,13 +57698,13 @@
         <v>9</v>
       </c>
       <c r="T121" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U121" t="n">
         <v>9</v>
       </c>
       <c r="V121" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W121" t="n">
         <v>13</v>
@@ -57879,10 +57879,10 @@
         <v>0.85</v>
       </c>
       <c r="CA121" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="CB121" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="CC121" t="n">
         <v>0</v>
@@ -58873,7 +58873,7 @@
         <v>26</v>
       </c>
       <c r="CS123" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="CT123" t="n">
         <v>1</v>
@@ -59117,10 +59117,10 @@
         <v>7</v>
       </c>
       <c r="Y124" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Z124" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
@@ -59574,13 +59574,13 @@
         <v>15</v>
       </c>
       <c r="T125" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U125" t="n">
         <v>17</v>
       </c>
       <c r="V125" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="W125" t="n">
         <v>16</v>
@@ -59755,10 +59755,10 @@
         <v>1.71</v>
       </c>
       <c r="CA125" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="CB125" t="n">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="CC125" t="n">
         <v>1</v>
@@ -60061,10 +60061,10 @@
         <v>12</v>
       </c>
       <c r="Y126" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Z126" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
@@ -60515,16 +60515,16 @@
         <v>2</v>
       </c>
       <c r="S127" t="n">
+        <v>14</v>
+      </c>
+      <c r="T127" t="n">
         <v>12</v>
       </c>
-      <c r="T127" t="n">
-        <v>11</v>
-      </c>
       <c r="U127" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="V127" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W127" t="n">
         <v>12</v>
@@ -60533,10 +60533,10 @@
         <v>13</v>
       </c>
       <c r="Y127" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Z127" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
@@ -60696,13 +60696,13 @@
         <v>129</v>
       </c>
       <c r="BZ127" t="n">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="CA127" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="CB127" t="n">
-        <v>2.82</v>
+        <v>3.01</v>
       </c>
       <c r="CC127" t="n">
         <v>0</v>

--- a/data/matches/leagues/Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/matches/leagues/Germany_Bundesliga_2_2025-2026.xlsx
@@ -60975,13 +60975,13 @@
         <v>2</v>
       </c>
       <c r="S128" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T128" t="n">
         <v>2</v>
       </c>
       <c r="U128" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="V128" t="n">
         <v>4</v>
@@ -61156,13 +61156,13 @@
         <v>92</v>
       </c>
       <c r="BZ128" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="CA128" t="n">
         <v>0.57</v>
       </c>
       <c r="CB128" t="n">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="CC128" t="n">
         <v>1</v>
@@ -61945,7 +61945,7 @@
         <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R130" t="n">
         <v>6</v>
@@ -61957,7 +61957,7 @@
         <v>9</v>
       </c>
       <c r="U130" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="V130" t="n">
         <v>15</v>
@@ -62132,13 +62132,13 @@
         <v>78</v>
       </c>
       <c r="BZ130" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="CA130" t="n">
         <v>1.6</v>
       </c>
       <c r="CB130" t="n">
-        <v>2.93</v>
+        <v>3.06</v>
       </c>
       <c r="CC130" t="n">
         <v>0</v>
@@ -63351,13 +63351,13 @@
         <v>3</v>
       </c>
       <c r="S133" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="T133" t="n">
         <v>7</v>
       </c>
       <c r="U133" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="V133" t="n">
         <v>10</v>
@@ -63532,13 +63532,13 @@
         <v>67</v>
       </c>
       <c r="BZ133" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="CA133" t="n">
         <v>1.15</v>
       </c>
       <c r="CB133" t="n">
-        <v>3.71</v>
+        <v>3.65</v>
       </c>
       <c r="CC133" t="n">
         <v>0</v>
@@ -63820,7 +63820,7 @@
         <v>3</v>
       </c>
       <c r="R134" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -63832,7 +63832,7 @@
         <v>13</v>
       </c>
       <c r="V134" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W134" t="n">
         <v>12</v>
@@ -64007,10 +64007,10 @@
         <v>1.46</v>
       </c>
       <c r="CA134" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="CB134" t="n">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="CC134" t="n">
         <v>0</v>
@@ -64292,19 +64292,19 @@
         <v>3</v>
       </c>
       <c r="R135" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S135" t="n">
         <v>17</v>
       </c>
       <c r="T135" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U135" t="n">
         <v>20</v>
       </c>
       <c r="V135" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="W135" t="n">
         <v>13</v>
@@ -64471,10 +64471,10 @@
         <v>1.82</v>
       </c>
       <c r="CA135" t="n">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="CB135" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="CC135" t="n">
         <v>1</v>
@@ -64540,7 +64540,7 @@
         <v>1</v>
       </c>
       <c r="CX135" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CY135" t="n">
         <v>10</v>

--- a/data/matches/leagues/Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/matches/leagues/Germany_Bundesliga_2_2025-2026.xlsx
@@ -66677,10 +66677,10 @@
         <v>8</v>
       </c>
       <c r="Y140" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Z140" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
@@ -67134,13 +67134,13 @@
         <v>10</v>
       </c>
       <c r="T141" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U141" t="n">
         <v>18</v>
       </c>
       <c r="V141" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W141" t="n">
         <v>11</v>
@@ -67149,10 +67149,10 @@
         <v>14</v>
       </c>
       <c r="Y141" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Z141" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
@@ -67315,10 +67315,10 @@
         <v>1.96</v>
       </c>
       <c r="CA141" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="CB141" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="CC141" t="n">
         <v>1</v>
@@ -67600,13 +67600,13 @@
         <v>7</v>
       </c>
       <c r="R142" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S142" t="n">
         <v>13</v>
       </c>
       <c r="T142" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U142" t="n">
         <v>20</v>
@@ -67787,10 +67787,10 @@
         <v>2.14</v>
       </c>
       <c r="CA142" t="n">
-        <v>0.96</v>
+        <v>1.03</v>
       </c>
       <c r="CB142" t="n">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="CC142" t="n">
         <v>0</v>
@@ -68807,7 +68807,7 @@
         <v>1</v>
       </c>
       <c r="CU144" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="CV144" t="n">
         <v>7</v>

--- a/data/matches/leagues/Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/matches/leagues/Germany_Bundesliga_2_2025-2026.xlsx
@@ -67603,13 +67603,13 @@
         <v>4</v>
       </c>
       <c r="S142" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="T142" t="n">
         <v>4</v>
       </c>
       <c r="U142" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="V142" t="n">
         <v>8</v>
@@ -67784,13 +67784,13 @@
         <v>91</v>
       </c>
       <c r="BZ142" t="n">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="CA142" t="n">
         <v>1.03</v>
       </c>
       <c r="CB142" t="n">
-        <v>3.17</v>
+        <v>3.29</v>
       </c>
       <c r="CC142" t="n">
         <v>0</v>
@@ -68560,13 +68560,13 @@
         <v>3</v>
       </c>
       <c r="R144" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S144" t="n">
         <v>12</v>
       </c>
       <c r="T144" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U144" t="n">
         <v>15</v>
@@ -68581,10 +68581,10 @@
         <v>20</v>
       </c>
       <c r="Y144" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Z144" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
@@ -68747,10 +68747,10 @@
         <v>1.53</v>
       </c>
       <c r="CA144" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="CB144" t="n">
-        <v>3.21</v>
+        <v>3.14</v>
       </c>
       <c r="CC144" t="n">
         <v>0</v>
@@ -69021,7 +69021,7 @@
         <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R145" t="n">
         <v>1</v>
@@ -69033,7 +69033,7 @@
         <v>14</v>
       </c>
       <c r="U145" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V145" t="n">
         <v>15</v>
@@ -69208,13 +69208,13 @@
         <v>122</v>
       </c>
       <c r="BZ145" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="CA145" t="n">
         <v>1.41</v>
       </c>
       <c r="CB145" t="n">
-        <v>2.91</v>
+        <v>3.04</v>
       </c>
       <c r="CC145" t="n">
         <v>0</v>

--- a/data/matches/leagues/Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/matches/leagues/Germany_Bundesliga_2_2025-2026.xlsx
@@ -69507,13 +69507,13 @@
         <v>2</v>
       </c>
       <c r="S146" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T146" t="n">
         <v>7</v>
       </c>
       <c r="U146" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V146" t="n">
         <v>9</v>
@@ -69688,13 +69688,13 @@
         <v>65</v>
       </c>
       <c r="BZ146" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="CA146" t="n">
         <v>0.88</v>
       </c>
       <c r="CB146" t="n">
-        <v>3.07</v>
+        <v>3.2</v>
       </c>
       <c r="CC146" t="n">
         <v>1</v>
@@ -70454,19 +70454,19 @@
         <v>7</v>
       </c>
       <c r="T148" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="U148" t="n">
         <v>11</v>
       </c>
       <c r="V148" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W148" t="n">
         <v>7</v>
       </c>
       <c r="X148" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y148" t="n">
         <v>37</v>
@@ -70635,10 +70635,10 @@
         <v>1.18</v>
       </c>
       <c r="CA148" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="CB148" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="CC148" t="n">
         <v>0</v>
@@ -71413,10 +71413,10 @@
         <v>5</v>
       </c>
       <c r="Y150" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Z150" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
@@ -72668,54 +72668,62 @@
       </c>
       <c r="DW152" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.98</t>
         </is>
       </c>
       <c r="DX152" t="inlineStr">
         <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="DY152" t="inlineStr"/>
-      <c r="DZ152" t="inlineStr"/>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="DY152" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="DZ152" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
       <c r="EA152" t="inlineStr">
         <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="EB152" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="EC152" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="ED152" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="EE152" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="EF152" t="inlineStr">
+        <is>
           <t>3.39</t>
         </is>
       </c>
-      <c r="EB152" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EC152" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="ED152" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="EE152" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
-      <c r="EF152" t="inlineStr">
-        <is>
-          <t>3.47</t>
-        </is>
-      </c>
       <c r="EG152" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EH152" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="EI152" t="n">
@@ -72734,16 +72742,24 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="EM152" t="inlineStr"/>
-      <c r="EN152" t="inlineStr"/>
+      <c r="EM152" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EN152" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
       <c r="EO152" t="inlineStr">
         <is>
-          <t>2.98</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="EP152" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.40</t>
         </is>
       </c>
     </row>
@@ -73145,57 +73161,45 @@
       </c>
       <c r="DX153" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="DY153" t="inlineStr">
         <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="DZ153" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EA153" t="inlineStr"/>
+      <c r="EB153" t="inlineStr"/>
+      <c r="EC153" t="inlineStr"/>
+      <c r="ED153" t="inlineStr">
+        <is>
+          <t>3.71</t>
+        </is>
+      </c>
+      <c r="EE153" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EF153" t="inlineStr">
+        <is>
+          <t>3.67</t>
+        </is>
+      </c>
+      <c r="EG153" t="inlineStr">
+        <is>
           <t>1.67</t>
         </is>
       </c>
-      <c r="DZ153" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="EA153" t="inlineStr">
-        <is>
-          <t>2.83</t>
-        </is>
-      </c>
-      <c r="EB153" t="inlineStr">
-        <is>
-          <t>1.79</t>
-        </is>
-      </c>
-      <c r="EC153" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="ED153" t="inlineStr">
-        <is>
-          <t>3.73</t>
-        </is>
-      </c>
-      <c r="EE153" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="EF153" t="inlineStr">
-        <is>
-          <t>3.64</t>
-        </is>
-      </c>
-      <c r="EG153" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
       <c r="EH153" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="EI153" t="n">
@@ -73216,8 +73220,16 @@
       </c>
       <c r="EM153" t="inlineStr"/>
       <c r="EN153" t="inlineStr"/>
-      <c r="EO153" t="inlineStr"/>
-      <c r="EP153" t="inlineStr"/>
+      <c r="EO153" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="EP153" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -73612,12 +73624,12 @@
       </c>
       <c r="DW154" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="DX154" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="DY154" t="inlineStr">
@@ -73632,42 +73644,42 @@
       </c>
       <c r="EA154" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="EB154" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EC154" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="ED154" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="EE154" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="EF154" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="EG154" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EH154" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="EI154" t="n">
@@ -73690,12 +73702,12 @@
       <c r="EN154" t="inlineStr"/>
       <c r="EO154" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="EP154" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.39</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/matches/leagues/Germany_Bundesliga_2_2025-2026.xlsx
@@ -73298,13 +73298,13 @@
         <v>12</v>
       </c>
       <c r="T154" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U154" t="n">
         <v>19</v>
       </c>
       <c r="V154" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W154" t="n">
         <v>19</v>
@@ -73479,10 +73479,10 @@
         <v>2.07</v>
       </c>
       <c r="CA154" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="CB154" t="n">
-        <v>3.4</v>
+        <v>3.46</v>
       </c>
       <c r="CC154" t="n">
         <v>0</v>

--- a/data/matches/leagues/Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/matches/leagues/Germany_Bundesliga_2_2025-2026.xlsx
@@ -36071,16 +36071,16 @@
         <v>5</v>
       </c>
       <c r="S75" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T75" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U75" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V75" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="W75" t="n">
         <v>12</v>
@@ -36252,13 +36252,13 @@
         <v>84</v>
       </c>
       <c r="BZ75" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="CA75" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="CB75" t="n">
-        <v>3.17</v>
+        <v>3.05</v>
       </c>
       <c r="CC75" t="n">
         <v>0</v>
@@ -37936,7 +37936,7 @@
         <v>3</v>
       </c>
       <c r="N79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -37988,7 +37988,7 @@
         <v>3</v>
       </c>
       <c r="AD79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE79" t="n">
         <v>2.5</v>
@@ -38108,13 +38108,13 @@
         <v>3</v>
       </c>
       <c r="BR79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS79" t="n">
         <v>0</v>
       </c>
       <c r="BT79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BU79" t="n">
         <v>1</v>
@@ -38849,7 +38849,7 @@
         <v>10</v>
       </c>
       <c r="M81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N81" t="n">
         <v>1</v>
@@ -38901,7 +38901,7 @@
         </is>
       </c>
       <c r="AC81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD81" t="n">
         <v>1</v>
@@ -39021,7 +39021,7 @@
         <v>0</v>
       </c>
       <c r="BQ81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BR81" t="n">
         <v>1</v>
@@ -39030,7 +39030,7 @@
         <v>0</v>
       </c>
       <c r="BT81" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BU81" t="n">
         <v>1</v>
@@ -40291,7 +40291,7 @@
         <v>7</v>
       </c>
       <c r="W84" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="X84" t="n">
         <v>13</v>
@@ -40526,7 +40526,7 @@
         <v>13</v>
       </c>
       <c r="CV84" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CW84" t="n">
         <v>1</v>
@@ -44500,7 +44500,7 @@
         <v>5</v>
       </c>
       <c r="N93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -44552,7 +44552,7 @@
         <v>5</v>
       </c>
       <c r="AD93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE93" t="n">
         <v>2.72</v>
@@ -44672,13 +44672,13 @@
         <v>2</v>
       </c>
       <c r="BR93" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS93" t="n">
         <v>4</v>
       </c>
       <c r="BT93" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BU93" t="n">
         <v>1</v>
@@ -45757,10 +45757,10 @@
         <v>1.61</v>
       </c>
       <c r="DM95" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="DN95" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="DO95" t="n">
         <v>17</v>
@@ -48086,13 +48086,13 @@
         <v>20</v>
       </c>
       <c r="DL100" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="DM100" t="n">
         <v>1.21</v>
       </c>
       <c r="DN100" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="DO100" t="n">
         <v>17</v>
@@ -48718,13 +48718,13 @@
         <v>5</v>
       </c>
       <c r="T102" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U102" t="n">
         <v>7</v>
       </c>
       <c r="V102" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="W102" t="n">
         <v>9</v>
@@ -48899,10 +48899,10 @@
         <v>0.89</v>
       </c>
       <c r="CA102" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="CB102" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="CC102" t="n">
         <v>0</v>
@@ -53229,10 +53229,10 @@
         <v>1.33</v>
       </c>
       <c r="DM111" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="DN111" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="DO111" t="n">
         <v>17</v>
@@ -53714,13 +53714,13 @@
         <v>25</v>
       </c>
       <c r="DL112" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="DM112" t="n">
         <v>1.59</v>
       </c>
       <c r="DN112" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="DO112" t="n">
         <v>17</v>
@@ -53877,13 +53877,13 @@
         <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R113" t="n">
         <v>6</v>
       </c>
       <c r="S113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T113" t="n">
         <v>8</v>
@@ -54064,13 +54064,13 @@
         <v>198</v>
       </c>
       <c r="BZ113" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="CA113" t="n">
         <v>1.89</v>
       </c>
       <c r="CB113" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="CC113" t="n">
         <v>0</v>
@@ -54118,7 +54118,7 @@
         <v>1</v>
       </c>
       <c r="CR113" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="CS113" t="n">
         <v>14</v>
@@ -54130,7 +54130,7 @@
         <v>20</v>
       </c>
       <c r="CV113" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CW113" t="n">
         <v>1</v>
@@ -55309,13 +55309,13 @@
         <v>1</v>
       </c>
       <c r="Q116" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R116" t="n">
         <v>2</v>
       </c>
       <c r="S116" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="T116" t="n">
         <v>6</v>
@@ -55496,13 +55496,13 @@
         <v>74</v>
       </c>
       <c r="BZ116" t="n">
-        <v>2.92</v>
+        <v>2.99</v>
       </c>
       <c r="CA116" t="n">
         <v>0.78</v>
       </c>
       <c r="CB116" t="n">
-        <v>3.69</v>
+        <v>3.76</v>
       </c>
       <c r="CC116" t="n">
         <v>0</v>
@@ -57695,13 +57695,13 @@
         <v>5</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T121" t="n">
         <v>5</v>
       </c>
       <c r="U121" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V121" t="n">
         <v>10</v>
@@ -57713,10 +57713,10 @@
         <v>18</v>
       </c>
       <c r="Y121" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Z121" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AA121" t="inlineStr"/>
       <c r="AB121" t="inlineStr"/>
@@ -57868,13 +57868,13 @@
         <v>108</v>
       </c>
       <c r="BZ121" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="CA121" t="n">
         <v>1.3</v>
       </c>
       <c r="CB121" t="n">
-        <v>3.02</v>
+        <v>3.08</v>
       </c>
       <c r="CC121" t="n">
         <v>0</v>
@@ -60801,10 +60801,10 @@
         <v>1.51</v>
       </c>
       <c r="DM127" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="DN127" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="DO127" t="n">
         <v>17</v>
@@ -61270,13 +61270,13 @@
         <v>7</v>
       </c>
       <c r="DL128" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="DM128" t="n">
         <v>1.67</v>
       </c>
       <c r="DN128" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="DO128" t="n">
         <v>17</v>
@@ -61758,13 +61758,13 @@
         <v>29</v>
       </c>
       <c r="DL129" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DM129" t="n">
         <v>1.43</v>
       </c>
       <c r="DN129" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="DO129" t="n">
         <v>17</v>
@@ -63182,13 +63182,13 @@
         <v>15</v>
       </c>
       <c r="DL132" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="DM132" t="n">
         <v>1.59</v>
       </c>
       <c r="DN132" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="DO132" t="n">
         <v>17</v>
@@ -64110,13 +64110,13 @@
         <v>15</v>
       </c>
       <c r="DL134" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="DM134" t="n">
         <v>1.25</v>
       </c>
       <c r="DN134" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="DO134" t="n">
         <v>17</v>
@@ -65537,10 +65537,10 @@
         <v>1.3</v>
       </c>
       <c r="DM137" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DN137" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="DO137" t="n">
         <v>17</v>
@@ -66187,13 +66187,13 @@
         <v>1</v>
       </c>
       <c r="S139" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T139" t="n">
         <v>3</v>
       </c>
       <c r="U139" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V139" t="n">
         <v>4</v>
@@ -66205,10 +66205,10 @@
         <v>10</v>
       </c>
       <c r="Y139" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Z139" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
@@ -66368,13 +66368,13 @@
         <v>37</v>
       </c>
       <c r="BZ139" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="CA139" t="n">
         <v>0.38</v>
       </c>
       <c r="CB139" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="CC139" t="n">
         <v>0</v>
@@ -71218,13 +71218,13 @@
         <v>25</v>
       </c>
       <c r="DL149" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DM149" t="n">
         <v>1.72</v>
       </c>
       <c r="DN149" t="n">
-        <v>3.62</v>
+        <v>3.63</v>
       </c>
       <c r="DO149" t="n">
         <v>17</v>
@@ -71867,13 +71867,13 @@
         <v>8</v>
       </c>
       <c r="S151" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T151" t="n">
         <v>11</v>
       </c>
       <c r="U151" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="V151" t="n">
         <v>19</v>
@@ -72048,13 +72048,13 @@
         <v>121</v>
       </c>
       <c r="BZ151" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="CA151" t="n">
         <v>2.14</v>
       </c>
       <c r="CB151" t="n">
-        <v>3.43</v>
+        <v>3.3</v>
       </c>
       <c r="CC151" t="n">
         <v>0</v>
@@ -72634,13 +72634,13 @@
         <v>19</v>
       </c>
       <c r="DL152" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="DM152" t="n">
         <v>1.45</v>
       </c>
       <c r="DN152" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="DO152" t="n">
         <v>17</v>
@@ -72830,13 +72830,13 @@
         <v>5</v>
       </c>
       <c r="T153" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U153" t="n">
         <v>10</v>
       </c>
       <c r="V153" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W153" t="n">
         <v>14</v>
@@ -73011,10 +73011,10 @@
         <v>1.17</v>
       </c>
       <c r="CA153" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="CB153" t="n">
-        <v>3.03</v>
+        <v>3.09</v>
       </c>
       <c r="CC153" t="n">
         <v>0</v>
@@ -73590,13 +73590,13 @@
         <v>13</v>
       </c>
       <c r="DL154" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DM154" t="n">
         <v>1.64</v>
       </c>
       <c r="DN154" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="DO154" t="n">
         <v>17</v>

--- a/data/matches/leagues/Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/matches/leagues/Germany_Bundesliga_2_2025-2026.xlsx
@@ -73772,7 +73772,7 @@
         <v>3</v>
       </c>
       <c r="R155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S155" t="n">
         <v>9</v>
@@ -73784,7 +73784,7 @@
         <v>12</v>
       </c>
       <c r="V155" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W155" t="n">
         <v>12</v>
@@ -73959,10 +73959,10 @@
         <v>1.39</v>
       </c>
       <c r="CA155" t="n">
-        <v>0.74</v>
+        <v>0.87</v>
       </c>
       <c r="CB155" t="n">
-        <v>2.13</v>
+        <v>2.26</v>
       </c>
       <c r="CC155" t="n">
         <v>0</v>
@@ -74697,13 +74697,13 @@
         <v>0</v>
       </c>
       <c r="Q157" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R157" t="n">
         <v>0</v>
       </c>
       <c r="S157" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T157" t="n">
         <v>9</v>
@@ -74876,13 +74876,13 @@
         <v>86</v>
       </c>
       <c r="BZ157" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="CA157" t="n">
         <v>0.79</v>
       </c>
       <c r="CB157" t="n">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="CC157" t="n">
         <v>0</v>
@@ -75175,13 +75175,13 @@
         <v>2</v>
       </c>
       <c r="S158" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T158" t="n">
         <v>12</v>
       </c>
       <c r="U158" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V158" t="n">
         <v>14</v>
@@ -75356,13 +75356,13 @@
         <v>84</v>
       </c>
       <c r="BZ158" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="CA158" t="n">
         <v>1.35</v>
       </c>
       <c r="CB158" t="n">
-        <v>3.11</v>
+        <v>3.04</v>
       </c>
       <c r="CC158" t="n">
         <v>0</v>
@@ -75650,13 +75650,13 @@
         <v>15</v>
       </c>
       <c r="T159" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U159" t="n">
         <v>27</v>
       </c>
       <c r="V159" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="W159" t="n">
         <v>10</v>
@@ -75665,10 +75665,10 @@
         <v>13</v>
       </c>
       <c r="Y159" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Z159" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
@@ -75831,10 +75831,10 @@
         <v>2.87</v>
       </c>
       <c r="CA159" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="CB159" t="n">
-        <v>4.42</v>
+        <v>4.36</v>
       </c>
       <c r="CC159" t="n">
         <v>0</v>
@@ -75900,7 +75900,7 @@
         <v>1</v>
       </c>
       <c r="CX159" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CY159" t="n">
         <v>10</v>
@@ -76121,19 +76121,19 @@
         <v>0</v>
       </c>
       <c r="Q160" t="n">
+        <v>7</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0</v>
+      </c>
+      <c r="S160" t="n">
         <v>6</v>
-      </c>
-      <c r="R160" t="n">
-        <v>0</v>
-      </c>
-      <c r="S160" t="n">
-        <v>5</v>
       </c>
       <c r="T160" t="n">
         <v>5</v>
       </c>
       <c r="U160" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="V160" t="n">
         <v>5</v>
@@ -76308,13 +76308,13 @@
         <v>83</v>
       </c>
       <c r="BZ160" t="n">
-        <v>1.54</v>
+        <v>1.73</v>
       </c>
       <c r="CA160" t="n">
         <v>0.47</v>
       </c>
       <c r="CB160" t="n">
-        <v>2.01</v>
+        <v>2.21</v>
       </c>
       <c r="CC160" t="n">
         <v>0</v>
@@ -76596,19 +76596,19 @@
         <v>3</v>
       </c>
       <c r="R161" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S161" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T161" t="n">
         <v>12</v>
       </c>
       <c r="U161" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V161" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W161" t="n">
         <v>12</v>
@@ -76780,13 +76780,13 @@
         <v>134</v>
       </c>
       <c r="BZ161" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="CA161" t="n">
-        <v>1.97</v>
+        <v>1.7</v>
       </c>
       <c r="CB161" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="CC161" t="n">
         <v>0</v>
@@ -77076,7 +77076,7 @@
         <v>6</v>
       </c>
       <c r="R162" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S162" t="n">
         <v>14</v>
@@ -77088,7 +77088,7 @@
         <v>20</v>
       </c>
       <c r="V162" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W162" t="n">
         <v>10</v>
@@ -77263,10 +77263,10 @@
         <v>2.19</v>
       </c>
       <c r="CA162" t="n">
-        <v>0.96</v>
+        <v>1.23</v>
       </c>
       <c r="CB162" t="n">
-        <v>3.15</v>
+        <v>3.42</v>
       </c>
       <c r="CC162" t="n">
         <v>0</v>
@@ -77559,13 +77559,13 @@
         <v>2</v>
       </c>
       <c r="S163" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T163" t="n">
         <v>9</v>
       </c>
       <c r="U163" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V163" t="n">
         <v>11</v>
@@ -77577,10 +77577,10 @@
         <v>14</v>
       </c>
       <c r="Y163" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Z163" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
@@ -77740,13 +77740,13 @@
         <v>89</v>
       </c>
       <c r="BZ163" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="CA163" t="n">
         <v>1.1</v>
       </c>
       <c r="CB163" t="n">
-        <v>3.03</v>
+        <v>2.97</v>
       </c>
       <c r="CC163" t="n">
         <v>0</v>

--- a/data/matches/leagues/Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/matches/leagues/Germany_Bundesliga_2_2025-2026.xlsx
@@ -78991,13 +78991,13 @@
         <v>2</v>
       </c>
       <c r="S166" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T166" t="n">
         <v>5</v>
       </c>
       <c r="U166" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V166" t="n">
         <v>7</v>
@@ -79172,13 +79172,13 @@
         <v>99</v>
       </c>
       <c r="BZ166" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="CA166" t="n">
         <v>0.86</v>
       </c>
       <c r="CB166" t="n">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="CC166" t="n">
         <v>0</v>
@@ -79940,13 +79940,13 @@
         <v>6</v>
       </c>
       <c r="R168" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="S168" t="n">
         <v>8</v>
       </c>
       <c r="T168" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U168" t="n">
         <v>14</v>
@@ -80127,10 +80127,10 @@
         <v>1.58</v>
       </c>
       <c r="CA168" t="n">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="CB168" t="n">
-        <v>3.63</v>
+        <v>3.7</v>
       </c>
       <c r="CC168" t="n">
         <v>0</v>
@@ -80178,7 +80178,7 @@
         <v>1</v>
       </c>
       <c r="CR168" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="CS168" t="n">
         <v>21</v>
@@ -80196,7 +80196,7 @@
         <v>1</v>
       </c>
       <c r="CX168" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="CY168" t="n">
         <v>5</v>
@@ -80433,10 +80433,10 @@
         <v>9</v>
       </c>
       <c r="Y169" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Z169" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
@@ -80879,13 +80879,13 @@
         <v>3</v>
       </c>
       <c r="S170" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T170" t="n">
         <v>4</v>
       </c>
       <c r="U170" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V170" t="n">
         <v>7</v>
@@ -81000,7 +81000,7 @@
         <v>0</v>
       </c>
       <c r="BF170" t="n">
-        <v>-1</v>
+        <v>9307</v>
       </c>
       <c r="BG170" t="n">
         <v>2</v>
@@ -81060,13 +81060,13 @@
         <v>87</v>
       </c>
       <c r="BZ170" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="CA170" t="n">
         <v>0.86</v>
       </c>
       <c r="CB170" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="CC170" t="n">
         <v>0</v>
@@ -81480,7 +81480,7 @@
         <v>0</v>
       </c>
       <c r="BF171" t="n">
-        <v>-1</v>
+        <v>62077</v>
       </c>
       <c r="BG171" t="n">
         <v>2</v>
@@ -81847,13 +81847,13 @@
         <v>2</v>
       </c>
       <c r="S172" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T172" t="n">
         <v>6</v>
       </c>
       <c r="U172" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="V172" t="n">
         <v>8</v>
@@ -81968,7 +81968,7 @@
         <v>0</v>
       </c>
       <c r="BF172" t="n">
-        <v>-1</v>
+        <v>14667</v>
       </c>
       <c r="BG172" t="n">
         <v>2</v>
@@ -82028,13 +82028,13 @@
         <v>43</v>
       </c>
       <c r="BZ172" t="n">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="CA172" t="n">
         <v>0.84</v>
       </c>
       <c r="CB172" t="n">
-        <v>3.82</v>
+        <v>3.88</v>
       </c>
       <c r="CC172" t="n">
         <v>0</v>

--- a/data/matches/leagues/Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/matches/leagues/Germany_Bundesliga_2_2025-2026.xlsx
@@ -80613,10 +80613,10 @@
         <v>9</v>
       </c>
       <c r="Y175" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Z175" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AA175" t="inlineStr"/>
       <c r="AB175" t="inlineStr"/>
@@ -81531,13 +81531,13 @@
         <v>2</v>
       </c>
       <c r="S177" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T177" t="n">
         <v>3</v>
       </c>
       <c r="U177" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V177" t="n">
         <v>5</v>
@@ -81549,10 +81549,10 @@
         <v>17</v>
       </c>
       <c r="Y177" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Z177" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AA177" t="inlineStr">
         <is>
@@ -81712,13 +81712,13 @@
         <v>74</v>
       </c>
       <c r="BZ177" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="CA177" t="n">
         <v>0.66</v>
       </c>
       <c r="CB177" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="CC177" t="n">
         <v>0</v>
@@ -82003,13 +82003,13 @@
         <v>9</v>
       </c>
       <c r="S178" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T178" t="n">
         <v>9</v>
       </c>
       <c r="U178" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V178" t="n">
         <v>18</v>
@@ -82184,13 +82184,13 @@
         <v>114</v>
       </c>
       <c r="BZ178" t="n">
-        <v>0.63</v>
+        <v>0.7</v>
       </c>
       <c r="CA178" t="n">
         <v>2.25</v>
       </c>
       <c r="CB178" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="CC178" t="n">
         <v>0</v>
@@ -83028,7 +83028,7 @@
         <v>0</v>
       </c>
       <c r="BF180" t="n">
-        <v>-1</v>
+        <v>35756</v>
       </c>
       <c r="BG180" t="n">
         <v>2</v>

--- a/data/matches/leagues/Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/matches/leagues/Germany_Bundesliga_2_2025-2026.xlsx
@@ -82000,19 +82000,19 @@
         <v>1</v>
       </c>
       <c r="R178" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S178" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T178" t="n">
         <v>9</v>
       </c>
       <c r="U178" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V178" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W178" t="n">
         <v>10</v>
@@ -82184,13 +82184,13 @@
         <v>114</v>
       </c>
       <c r="BZ178" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="CA178" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="CB178" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="CC178" t="n">
         <v>0</v>
@@ -82907,16 +82907,16 @@
         <v>4</v>
       </c>
       <c r="S180" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T180" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U180" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V180" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="W180" t="n">
         <v>9</v>
@@ -82925,10 +82925,10 @@
         <v>15</v>
       </c>
       <c r="Y180" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Z180" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
@@ -83088,10 +83088,10 @@
         <v>120</v>
       </c>
       <c r="BZ180" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="CA180" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="CB180" t="n">
         <v>3.09</v>
@@ -83379,13 +83379,13 @@
         <v>4</v>
       </c>
       <c r="S181" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T181" t="n">
         <v>6</v>
       </c>
       <c r="U181" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V181" t="n">
         <v>10</v>
@@ -83560,13 +83560,13 @@
         <v>89</v>
       </c>
       <c r="BZ181" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="CA181" t="n">
         <v>1.14</v>
       </c>
       <c r="CB181" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="CC181" t="n">
         <v>0</v>

--- a/data/matches/leagues/Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/matches/leagues/Germany_Bundesliga_2_2025-2026.xlsx
@@ -86567,13 +86567,13 @@
         <v>5</v>
       </c>
       <c r="S188" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T188" t="n">
         <v>14</v>
       </c>
       <c r="U188" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V188" t="n">
         <v>19</v>
@@ -86748,13 +86748,13 @@
         <v>90</v>
       </c>
       <c r="BZ188" t="n">
-        <v>0.91</v>
+        <v>1.03</v>
       </c>
       <c r="CA188" t="n">
         <v>1.8</v>
       </c>
       <c r="CB188" t="n">
-        <v>2.71</v>
+        <v>2.83</v>
       </c>
       <c r="CC188" t="n">
         <v>0</v>
@@ -87023,16 +87023,16 @@
         <v>4</v>
       </c>
       <c r="S189" t="n">
+        <v>13</v>
+      </c>
+      <c r="T189" t="n">
+        <v>8</v>
+      </c>
+      <c r="U189" t="n">
+        <v>21</v>
+      </c>
+      <c r="V189" t="n">
         <v>12</v>
-      </c>
-      <c r="T189" t="n">
-        <v>6</v>
-      </c>
-      <c r="U189" t="n">
-        <v>20</v>
-      </c>
-      <c r="V189" t="n">
-        <v>10</v>
       </c>
       <c r="W189" t="n">
         <v>14</v>
@@ -87204,13 +87204,13 @@
         <v>120</v>
       </c>
       <c r="BZ189" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="CA189" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="CB189" t="n">
-        <v>3.45</v>
+        <v>3.64</v>
       </c>
       <c r="CC189" t="n">
         <v>0</v>

--- a/data/matches/leagues/Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/matches/leagues/Germany_Bundesliga_2_2025-2026.xlsx
@@ -90680,7 +90680,7 @@
         <v>4</v>
       </c>
       <c r="R197" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="S197" t="n">
         <v>6</v>
@@ -90692,7 +90692,7 @@
         <v>10</v>
       </c>
       <c r="V197" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="W197" t="n">
         <v>17</v>
@@ -90701,10 +90701,10 @@
         <v>10</v>
       </c>
       <c r="Y197" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Z197" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
@@ -90867,10 +90867,10 @@
         <v>1.29</v>
       </c>
       <c r="CA197" t="n">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="CB197" t="n">
-        <v>3.61</v>
+        <v>3.74</v>
       </c>
       <c r="CC197" t="n">
         <v>1</v>
@@ -91142,13 +91142,13 @@
         <v>13</v>
       </c>
       <c r="T198" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U198" t="n">
         <v>22</v>
       </c>
       <c r="V198" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W198" t="n">
         <v>16</v>
@@ -91323,10 +91323,10 @@
         <v>2.39</v>
       </c>
       <c r="CA198" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="CB198" t="n">
-        <v>3.27</v>
+        <v>3.21</v>
       </c>
       <c r="CC198" t="n">
         <v>0</v>

--- a/data/matches/leagues/Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/matches/leagues/Germany_Bundesliga_2_2025-2026.xlsx
@@ -94325,7 +94325,7 @@
         <v>0</v>
       </c>
       <c r="Q205" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R205" t="n">
         <v>4</v>
@@ -94337,7 +94337,7 @@
         <v>11</v>
       </c>
       <c r="U205" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="V205" t="n">
         <v>15</v>
@@ -94512,13 +94512,13 @@
         <v>90</v>
       </c>
       <c r="BZ205" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="CA205" t="n">
         <v>1.36</v>
       </c>
       <c r="CB205" t="n">
-        <v>4.15</v>
+        <v>4.02</v>
       </c>
       <c r="CC205" t="n">
         <v>1</v>
@@ -94784,19 +94784,19 @@
         <v>3</v>
       </c>
       <c r="R206" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S206" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T206" t="n">
         <v>4</v>
       </c>
       <c r="U206" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="V206" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W206" t="n">
         <v>17</v>
@@ -94805,10 +94805,10 @@
         <v>14</v>
       </c>
       <c r="Y206" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Z206" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
@@ -94968,13 +94968,13 @@
         <v>86</v>
       </c>
       <c r="BZ206" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="CA206" t="n">
-        <v>0.76</v>
+        <v>0.63</v>
       </c>
       <c r="CB206" t="n">
-        <v>2.06</v>
+        <v>1.87</v>
       </c>
       <c r="CC206" t="n">
         <v>0</v>
@@ -95253,10 +95253,10 @@
         <v>4</v>
       </c>
       <c r="Y207" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Z207" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AA207" t="inlineStr">
         <is>
@@ -95680,19 +95680,19 @@
         <v>8</v>
       </c>
       <c r="R208" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S208" t="n">
+        <v>11</v>
+      </c>
+      <c r="T208" t="n">
         <v>12</v>
       </c>
-      <c r="T208" t="n">
-        <v>10</v>
-      </c>
       <c r="U208" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="V208" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W208" t="n">
         <v>16</v>
@@ -95864,13 +95864,13 @@
         <v>78</v>
       </c>
       <c r="BZ208" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="CA208" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CB208" t="n">
-        <v>4.02</v>
+        <v>3.95</v>
       </c>
       <c r="CC208" t="n">
         <v>0</v>

--- a/data/matches/leagues/Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/matches/leagues/Germany_Bundesliga_2_2025-2026.xlsx
@@ -102095,13 +102095,13 @@
         <v>7</v>
       </c>
       <c r="S222" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T222" t="n">
         <v>10</v>
       </c>
       <c r="U222" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V222" t="n">
         <v>17</v>
@@ -102276,13 +102276,13 @@
         <v>90</v>
       </c>
       <c r="BZ222" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="CA222" t="n">
         <v>1.94</v>
       </c>
       <c r="CB222" t="n">
-        <v>2.95</v>
+        <v>3.02</v>
       </c>
       <c r="CC222" t="n">
         <v>0</v>
@@ -103456,16 +103456,16 @@
         <v>4</v>
       </c>
       <c r="R225" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S225" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T225" t="n">
+        <v>9</v>
+      </c>
+      <c r="U225" t="n">
         <v>10</v>
-      </c>
-      <c r="U225" t="n">
-        <v>11</v>
       </c>
       <c r="V225" t="n">
         <v>15</v>
@@ -103640,13 +103640,13 @@
         <v>103</v>
       </c>
       <c r="BZ225" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="CA225" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="CB225" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CC225" t="n">
         <v>0</v>
